--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_2705.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_2705.xlsx
@@ -1919,6 +1919,9 @@
           <t>2705-04-02</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>0.43</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>2705-04-02</t>
@@ -1931,12 +1934,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1956,6 +1959,9 @@
           <t>2705-LN-04-02</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>0.43</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>2705-LN-04-02</t>
@@ -1968,12 +1974,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1993,6 +1999,9 @@
           <t>2705-LN-06-04</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>0.57</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>2705-LN-06-04</t>
@@ -2005,12 +2014,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
